--- a/etf_holdings/2026-08-25_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:34</t>
+          <t>2026-08-25 10:25:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:34</t>
+          <t>2026-08-25 10:25:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:34</t>
+          <t>2026-08-25 10:25:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:34</t>
+          <t>2026-08-25 10:25:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:34</t>
+          <t>2026-08-25 10:25:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:34</t>
+          <t>2026-08-25 10:25:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:35</t>
+          <t>2026-08-25 10:25:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:35</t>
+          <t>2026-08-25 10:25:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:35</t>
+          <t>2026-08-25 10:25:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:35</t>
+          <t>2026-08-25 10:25:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:36</t>
+          <t>2026-08-25 10:25:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:36</t>
+          <t>2026-08-25 10:25:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:36</t>
+          <t>2026-08-25 10:25:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:36</t>
+          <t>2026-08-25 10:25:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:36</t>
+          <t>2026-08-25 10:25:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:36</t>
+          <t>2026-08-25 10:25:24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/etf_holdings/2026-08-25_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:21</t>
+          <t>2026-08-25 17:37:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:21</t>
+          <t>2026-08-25 17:37:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:21</t>
+          <t>2026-08-25 17:37:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,17 +635,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.92%1075</t>
+          <t>+1.86%1095</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:21</t>
+          <t>2026-08-25 17:37:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-4.4%5430</t>
+          <t>+3.04%5595</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>+3.04%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:21</t>
+          <t>2026-08-25 17:37:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.45%2375</t>
+          <t>+1.05%2400</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:21</t>
+          <t>2026-08-25 17:37:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:22</t>
+          <t>2026-08-25 17:37:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.86%1735</t>
+          <t>-1.44%1710</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:22</t>
+          <t>2026-08-25 17:37:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:22</t>
+          <t>2026-08-25 17:37:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.68%1455</t>
+          <t>+2.06%1485</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>+2.06%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:22</t>
+          <t>2026-08-25 17:37:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.66%3765</t>
+          <t>-0.8%3735</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:24</t>
+          <t>2026-08-25 17:37:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.83%5565</t>
+          <t>+0.63%5600</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:24</t>
+          <t>2026-08-25 17:37:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.85%592</t>
+          <t>-0.17%591</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:24</t>
+          <t>2026-08-25 17:37:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+1.72%2070</t>
+          <t>-1.93%2030</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:24</t>
+          <t>2026-08-25 17:37:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:24</t>
+          <t>2026-08-25 17:37:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0%1135</t>
+          <t>+2.2%1160</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25:24</t>
+          <t>2026-08-25 17:37:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+3.02%239</t>
+          <t>+0.21%239.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+3.02%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>239.5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">

--- a/etf_holdings/2026-08-25_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:57</t>
+          <t>2026-08-25 19:52:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:57</t>
+          <t>2026-08-25 19:52:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:57</t>
+          <t>2026-08-25 19:52:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:57</t>
+          <t>2026-08-25 19:52:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:57</t>
+          <t>2026-08-25 19:52:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:57</t>
+          <t>2026-08-25 19:52:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:58</t>
+          <t>2026-08-25 19:52:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:58</t>
+          <t>2026-08-25 19:52:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:58</t>
+          <t>2026-08-25 19:52:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:58</t>
+          <t>2026-08-25 19:52:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:59</t>
+          <t>2026-08-25 19:52:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:59</t>
+          <t>2026-08-25 19:52:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:59</t>
+          <t>2026-08-25 19:52:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:59</t>
+          <t>2026-08-25 19:52:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:59</t>
+          <t>2026-08-25 19:52:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:59</t>
+          <t>2026-08-25 19:52:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/etf_holdings/2026-08-25_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:46</t>
+          <t>2026-08-25 21:10:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:46</t>
+          <t>2026-08-25 21:10:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:46</t>
+          <t>2026-08-25 21:10:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:46</t>
+          <t>2026-08-25 21:10:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:46</t>
+          <t>2026-08-25 21:10:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:46</t>
+          <t>2026-08-25 21:10:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:47</t>
+          <t>2026-08-25 21:10:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:47</t>
+          <t>2026-08-25 21:10:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:47</t>
+          <t>2026-08-25 21:10:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:47</t>
+          <t>2026-08-25 21:10:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:48</t>
+          <t>2026-08-25 21:10:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:48</t>
+          <t>2026-08-25 21:10:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:48</t>
+          <t>2026-08-25 21:10:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:48</t>
+          <t>2026-08-25 21:10:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:48</t>
+          <t>2026-08-25 21:10:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 19:52:48</t>
+          <t>2026-08-25 21:10:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/etf_holdings/2026-08-25_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:18</t>
+          <t>2026-08-25 21:29:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:18</t>
+          <t>2026-08-25 21:29:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:18</t>
+          <t>2026-08-25 21:29:44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:18</t>
+          <t>2026-08-25 21:29:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:18</t>
+          <t>2026-08-25 21:29:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:18</t>
+          <t>2026-08-25 21:29:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:20</t>
+          <t>2026-08-25 21:29:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:20</t>
+          <t>2026-08-25 21:29:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:20</t>
+          <t>2026-08-25 21:29:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:20</t>
+          <t>2026-08-25 21:29:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:21</t>
+          <t>2026-08-25 21:29:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:21</t>
+          <t>2026-08-25 21:29:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:21</t>
+          <t>2026-08-25 21:29:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:21</t>
+          <t>2026-08-25 21:29:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:21</t>
+          <t>2026-08-25 21:29:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:10:21</t>
+          <t>2026-08-25 21:29:46</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/etf_holdings/2026-08-25_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:44</t>
+          <t>2026-08-25 21:32:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:44</t>
+          <t>2026-08-25 21:32:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:44</t>
+          <t>2026-08-25 21:32:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:44</t>
+          <t>2026-08-25 21:32:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:44</t>
+          <t>2026-08-25 21:32:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:44</t>
+          <t>2026-08-25 21:32:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:45</t>
+          <t>2026-08-25 21:32:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:45</t>
+          <t>2026-08-25 21:32:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:45</t>
+          <t>2026-08-25 21:32:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:45</t>
+          <t>2026-08-25 21:32:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:46</t>
+          <t>2026-08-25 21:32:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:46</t>
+          <t>2026-08-25 21:32:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:46</t>
+          <t>2026-08-25 21:32:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:46</t>
+          <t>2026-08-25 21:32:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:46</t>
+          <t>2026-08-25 21:32:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:29:46</t>
+          <t>2026-08-25 21:32:18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/etf_holdings/2026-08-25_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:15</t>
+          <t>2026-08-25 22:04:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:15</t>
+          <t>2026-08-25 22:04:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:15</t>
+          <t>2026-08-25 22:04:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:15</t>
+          <t>2026-08-25 22:04:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:15</t>
+          <t>2026-08-25 22:04:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:15</t>
+          <t>2026-08-25 22:04:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:17</t>
+          <t>2026-08-25 22:04:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:17</t>
+          <t>2026-08-25 22:04:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:17</t>
+          <t>2026-08-25 22:04:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:17</t>
+          <t>2026-08-25 22:04:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:18</t>
+          <t>2026-08-25 22:05:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:18</t>
+          <t>2026-08-25 22:05:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:18</t>
+          <t>2026-08-25 22:05:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:18</t>
+          <t>2026-08-25 22:05:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:18</t>
+          <t>2026-08-25 22:05:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:32:18</t>
+          <t>2026-08-25 22:05:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
